--- a/templates/cs_form_212.xlsx
+++ b/templates/cs_form_212.xlsx
@@ -15211,7 +15211,7 @@
       <headerFooter alignWithMargins="0"/>
     </customSheetView>
   </customSheetViews>
-  <mergeCells count="143">
+  <mergeCells count="142">
     <mergeCell ref="A61:N61"/>
     <mergeCell ref="A60:C60"/>
     <mergeCell ref="A59:N59"/>
@@ -15315,8 +15315,7 @@
     <mergeCell ref="L29:N29"/>
     <mergeCell ref="I18:K18"/>
     <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="I24:N24"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="D32:F32"/>
     <mergeCell ref="I25:K25"/>
